--- a/basedatos_partidas/salida/descompuestos/05.09.01.070.xlsx
+++ b/basedatos_partidas/salida/descompuestos/05.09.01.070.xlsx
@@ -662,10 +662,10 @@
         <v>0.4</v>
       </c>
       <c r="G14" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>171.59</v>
+        <v>171.91</v>
       </c>
     </row>
     <row r="17">
@@ -925,7 +925,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>199.68</v>
+        <v>200</v>
       </c>
       <c r="H28" t="n">
         <v>2</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="5" t="n">
-        <v>201.68</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
